--- a/backend/arq/search_tracks_one_dance.xlsx
+++ b/backend/arq/search_tracks_one_dance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="156">
   <si>
     <t>artists</t>
   </si>
@@ -100,9 +100,6 @@
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/3TVXtAsR1Inumwj472S9r4'}, 'href': 'https://api.spotify.com/v1/artists/3TVXtAsR1Inumwj472S9r4', 'id': '3TVXtAsR1Inumwj472S9r4', 'name': 'Drake', 'type': 'artist', 'uri': 'spotify:artist:3TVXtAsR1Inumwj472S9r4'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/3tVQdUvClmAT7URs9V3rsp'}, 'href': 'https://api.spotify.com/v1/artists/3tVQdUvClmAT7URs9V3rsp', 'id': '3tVQdUvClmAT7URs9V3rsp', 'name': 'Wizkid', 'type': 'artist', 'uri': 'spotify:artist:3tVQdUvClmAT7URs9V3rsp'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/6TK7fjRPdy2GW2pJzNF23L'}, 'href': 'https://api.spotify.com/v1/artists/6TK7fjRPdy2GW2pJzNF23L', 'id': '6TK7fjRPdy2GW2pJzNF23L', 'name': 'Kyla', 'type': 'artist', 'uri': 'spotify:artist:6TK7fjRPdy2GW2pJzNF23L'}]</t>
   </si>
   <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/6Ip8FS7vWT1uKkJSweANQK'}, 'href': 'https://api.spotify.com/v1/artists/6Ip8FS7vWT1uKkJSweANQK', 'id': '6Ip8FS7vWT1uKkJSweANQK', 'name': 'Dave', 'type': 'artist', 'uri': 'spotify:artist:6Ip8FS7vWT1uKkJSweANQK'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/687cZJR45JO7jhk1LHIbgq'}, 'href': 'https://api.spotify.com/v1/artists/687cZJR45JO7jhk1LHIbgq', 'id': '687cZJR45JO7jhk1LHIbgq', 'name': 'Tems', 'type': 'artist', 'uri': 'spotify:artist:687cZJR45JO7jhk1LHIbgq'}]</t>
-  </si>
-  <si>
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/5pKCCKE2ajJHZ9KAiaK11H'}, 'href': 'https://api.spotify.com/v1/artists/5pKCCKE2ajJHZ9KAiaK11H', 'id': '5pKCCKE2ajJHZ9KAiaK11H', 'name': 'Rihanna', 'type': 'artist', 'uri': 'spotify:artist:5pKCCKE2ajJHZ9KAiaK11H'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/3TVXtAsR1Inumwj472S9r4'}, 'href': 'https://api.spotify.com/v1/artists/3TVXtAsR1Inumwj472S9r4', 'id': '3TVXtAsR1Inumwj472S9r4', 'name': 'Drake', 'type': 'artist', 'uri': 'spotify:artist:3TVXtAsR1Inumwj472S9r4'}]</t>
   </si>
   <si>
@@ -115,150 +112,150 @@
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/16R2MLhKVi8GXUYSW8WoXD'}, 'href': 'https://api.spotify.com/v1/artists/16R2MLhKVi8GXUYSW8WoXD', 'id': '16R2MLhKVi8GXUYSW8WoXD', 'name': 'Fironn', 'type': 'artist', 'uri': 'spotify:artist:16R2MLhKVi8GXUYSW8WoXD'}]</t>
   </si>
   <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1uNFoZAHBGtllmzznpCI3s'}, 'href': 'https://api.spotify.com/v1/artists/1uNFoZAHBGtllmzznpCI3s', 'id': '1uNFoZAHBGtllmzznpCI3s', 'name': 'Justin Bieber', 'type': 'artist', 'uri': 'spotify:artist:1uNFoZAHBGtllmzznpCI3s'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/1anyVhU62p31KFi8MEzkbf'}, 'href': 'https://api.spotify.com/v1/artists/1anyVhU62p31KFi8MEzkbf', 'id': '1anyVhU62p31KFi8MEzkbf', 'name': 'Chance the Rapper', 'type': 'artist', 'uri': 'spotify:artist:1anyVhU62p31KFi8MEzkbf'}]</t>
+  </si>
+  <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1sPYSDiyubB8fkWvh3iFdr'}, 'href': 'https://api.spotify.com/v1/artists/1sPYSDiyubB8fkWvh3iFdr', 'id': '1sPYSDiyubB8fkWvh3iFdr', 'name': 'Leo Walt', 'type': 'artist', 'uri': 'spotify:artist:1sPYSDiyubB8fkWvh3iFdr'}]</t>
+  </si>
+  <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/3BWaTyIRQj4KFTCHwvLyHR'}, 'href': 'https://api.spotify.com/v1/artists/3BWaTyIRQj4KFTCHwvLyHR', 'id': '3BWaTyIRQj4KFTCHwvLyHR', 'name': 'POOL KIDS', 'type': 'artist', 'uri': 'spotify:artist:3BWaTyIRQj4KFTCHwvLyHR'}]</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/1zi7xx7UVEFkmKfv06H8x0</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/72TFWvU3wUYdUuxejTTIzt</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/6DCZcSspjsKoFjzjrWoCdn</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/0wwPcA6wtMf6HUMpIRdeP7</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/4upoy5cUKtXPwVgeMLQ4St</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/5ZKG94fnjiuMH5yrC5S9lS</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/1OJlaqFVhBObOIY5h9gRGO</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/3JsydWaf2Ev4ehaLUjj3SY</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/5JytDbvbXv4Ms68VSPgOve</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/tracks/2StjDIpRLEKBHcOGsZ2bk1</t>
+  </si>
+  <si>
+    <t>1zi7xx7UVEFkmKfv06H8x0</t>
+  </si>
+  <si>
+    <t>72TFWvU3wUYdUuxejTTIzt</t>
+  </si>
+  <si>
+    <t>6DCZcSspjsKoFjzjrWoCdn</t>
+  </si>
+  <si>
+    <t>0wwPcA6wtMf6HUMpIRdeP7</t>
+  </si>
+  <si>
+    <t>4upoy5cUKtXPwVgeMLQ4St</t>
+  </si>
+  <si>
+    <t>5ZKG94fnjiuMH5yrC5S9lS</t>
+  </si>
+  <si>
+    <t>1OJlaqFVhBObOIY5h9gRGO</t>
+  </si>
+  <si>
+    <t>3JsydWaf2Ev4ehaLUjj3SY</t>
+  </si>
+  <si>
+    <t>5JytDbvbXv4Ms68VSPgOve</t>
+  </si>
+  <si>
+    <t>2StjDIpRLEKBHcOGsZ2bk1</t>
+  </si>
+  <si>
+    <t>One Dance</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>God's Plan</t>
+  </si>
+  <si>
+    <t>Hotline Bling</t>
+  </si>
+  <si>
+    <t>One Dance - Slowed &amp; Reverb</t>
+  </si>
+  <si>
+    <t>One Dance - Instrumental Best Part Slowed</t>
+  </si>
+  <si>
+    <t>Confident</t>
+  </si>
+  <si>
+    <t>track</t>
+  </si>
+  <si>
+    <t>spotify:track:1zi7xx7UVEFkmKfv06H8x0</t>
+  </si>
+  <si>
+    <t>spotify:track:72TFWvU3wUYdUuxejTTIzt</t>
+  </si>
+  <si>
+    <t>spotify:track:6DCZcSspjsKoFjzjrWoCdn</t>
+  </si>
+  <si>
+    <t>spotify:track:0wwPcA6wtMf6HUMpIRdeP7</t>
+  </si>
+  <si>
+    <t>spotify:track:4upoy5cUKtXPwVgeMLQ4St</t>
+  </si>
+  <si>
+    <t>spotify:track:5ZKG94fnjiuMH5yrC5S9lS</t>
+  </si>
+  <si>
+    <t>spotify:track:1OJlaqFVhBObOIY5h9gRGO</t>
+  </si>
+  <si>
+    <t>spotify:track:3JsydWaf2Ev4ehaLUjj3SY</t>
+  </si>
+  <si>
+    <t>spotify:track:5JytDbvbXv4Ms68VSPgOve</t>
+  </si>
+  <si>
+    <t>spotify:track:2StjDIpRLEKBHcOGsZ2bk1</t>
+  </si>
+  <si>
+    <t>album</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/5pKCCKE2ajJHZ9KAiaK11H'}, 'href': 'https://api.spotify.com/v1/artists/5pKCCKE2ajJHZ9KAiaK11H', 'id': '5pKCCKE2ajJHZ9KAiaK11H', 'name': 'Rihanna', 'type': 'artist', 'uri': 'spotify:artist:5pKCCKE2ajJHZ9KAiaK11H'}]</t>
+  </si>
+  <si>
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1uNFoZAHBGtllmzznpCI3s'}, 'href': 'https://api.spotify.com/v1/artists/1uNFoZAHBGtllmzznpCI3s', 'id': '1uNFoZAHBGtllmzznpCI3s', 'name': 'Justin Bieber', 'type': 'artist', 'uri': 'spotify:artist:1uNFoZAHBGtllmzznpCI3s'}]</t>
   </si>
   <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1sPYSDiyubB8fkWvh3iFdr'}, 'href': 'https://api.spotify.com/v1/artists/1sPYSDiyubB8fkWvh3iFdr', 'id': '1sPYSDiyubB8fkWvh3iFdr', 'name': 'Leo Walt', 'type': 'artist', 'uri': 'spotify:artist:1sPYSDiyubB8fkWvh3iFdr'}]</t>
-  </si>
-  <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/3BWaTyIRQj4KFTCHwvLyHR'}, 'href': 'https://api.spotify.com/v1/artists/3BWaTyIRQj4KFTCHwvLyHR', 'id': '3BWaTyIRQj4KFTCHwvLyHR', 'name': 'POOL KIDS', 'type': 'artist', 'uri': 'spotify:artist:3BWaTyIRQj4KFTCHwvLyHR'}]</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/1zi7xx7UVEFkmKfv06H8x0</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/3oTuTpF1F3A7rEC6RKsMRz</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/72TFWvU3wUYdUuxejTTIzt</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/0wwPcA6wtMf6HUMpIRdeP7</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/4upoy5cUKtXPwVgeMLQ4St</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/5ZKG94fnjiuMH5yrC5S9lS</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/1OJlaqFVhBObOIY5h9gRGO</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/6eDApnV9Jdb1nYahOlbbUh</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/5JytDbvbXv4Ms68VSPgOve</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/tracks/2StjDIpRLEKBHcOGsZ2bk1</t>
-  </si>
-  <si>
-    <t>1zi7xx7UVEFkmKfv06H8x0</t>
-  </si>
-  <si>
-    <t>3oTuTpF1F3A7rEC6RKsMRz</t>
-  </si>
-  <si>
-    <t>72TFWvU3wUYdUuxejTTIzt</t>
-  </si>
-  <si>
-    <t>0wwPcA6wtMf6HUMpIRdeP7</t>
-  </si>
-  <si>
-    <t>4upoy5cUKtXPwVgeMLQ4St</t>
-  </si>
-  <si>
-    <t>5ZKG94fnjiuMH5yrC5S9lS</t>
-  </si>
-  <si>
-    <t>1OJlaqFVhBObOIY5h9gRGO</t>
-  </si>
-  <si>
-    <t>6eDApnV9Jdb1nYahOlbbUh</t>
-  </si>
-  <si>
-    <t>5JytDbvbXv4Ms68VSPgOve</t>
-  </si>
-  <si>
-    <t>2StjDIpRLEKBHcOGsZ2bk1</t>
-  </si>
-  <si>
-    <t>One Dance</t>
-  </si>
-  <si>
-    <t>Raindance (feat. Tems)</t>
-  </si>
-  <si>
-    <t>Work</t>
-  </si>
-  <si>
-    <t>Hotline Bling</t>
-  </si>
-  <si>
-    <t>One Dance - Slowed &amp; Reverb</t>
-  </si>
-  <si>
-    <t>One Dance - Instrumental Best Part Slowed</t>
-  </si>
-  <si>
-    <t>One Time</t>
-  </si>
-  <si>
-    <t>track</t>
-  </si>
-  <si>
-    <t>spotify:track:1zi7xx7UVEFkmKfv06H8x0</t>
-  </si>
-  <si>
-    <t>spotify:track:3oTuTpF1F3A7rEC6RKsMRz</t>
-  </si>
-  <si>
-    <t>spotify:track:72TFWvU3wUYdUuxejTTIzt</t>
-  </si>
-  <si>
-    <t>spotify:track:0wwPcA6wtMf6HUMpIRdeP7</t>
-  </si>
-  <si>
-    <t>spotify:track:4upoy5cUKtXPwVgeMLQ4St</t>
-  </si>
-  <si>
-    <t>spotify:track:5ZKG94fnjiuMH5yrC5S9lS</t>
-  </si>
-  <si>
-    <t>spotify:track:1OJlaqFVhBObOIY5h9gRGO</t>
-  </si>
-  <si>
-    <t>spotify:track:6eDApnV9Jdb1nYahOlbbUh</t>
-  </si>
-  <si>
-    <t>spotify:track:5JytDbvbXv4Ms68VSPgOve</t>
-  </si>
-  <si>
-    <t>spotify:track:2StjDIpRLEKBHcOGsZ2bk1</t>
-  </si>
-  <si>
-    <t>album</t>
-  </si>
-  <si>
-    <t>single</t>
-  </si>
-  <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/6Ip8FS7vWT1uKkJSweANQK'}, 'href': 'https://api.spotify.com/v1/artists/6Ip8FS7vWT1uKkJSweANQK', 'id': '6Ip8FS7vWT1uKkJSweANQK', 'name': 'Dave', 'type': 'artist', 'uri': 'spotify:artist:6Ip8FS7vWT1uKkJSweANQK'}]</t>
-  </si>
-  <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/5pKCCKE2ajJHZ9KAiaK11H'}, 'href': 'https://api.spotify.com/v1/artists/5pKCCKE2ajJHZ9KAiaK11H', 'id': '5pKCCKE2ajJHZ9KAiaK11H', 'name': 'Rihanna', 'type': 'artist', 'uri': 'spotify:artist:5pKCCKE2ajJHZ9KAiaK11H'}]</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/album/40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
-    <t>https://open.spotify.com/album/24f1GFXCkViGoRpmGqlSSl</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/album/4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
+    <t>https://open.spotify.com/album/1ATL5GLyefJaxhQzSPVrLX</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/album/1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -268,7 +265,7 @@
     <t>https://open.spotify.com/album/59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>https://open.spotify.com/album/1rG5TDs3jYh6OU753I54CI</t>
+    <t>https://open.spotify.com/album/1rknZw4cyL9NInAqSwc8AA</t>
   </si>
   <si>
     <t>https://open.spotify.com/album/0OlIvZ79fagLF0PMAiPi3m</t>
@@ -280,12 +277,12 @@
     <t>https://api.spotify.com/v1/albums/40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/albums/24f1GFXCkViGoRpmGqlSSl</t>
-  </si>
-  <si>
     <t>https://api.spotify.com/v1/albums/4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/albums/1ATL5GLyefJaxhQzSPVrLX</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/albums/1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -295,7 +292,7 @@
     <t>https://api.spotify.com/v1/albums/59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/albums/1rG5TDs3jYh6OU753I54CI</t>
+    <t>https://api.spotify.com/v1/albums/1rknZw4cyL9NInAqSwc8AA</t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/albums/0OlIvZ79fagLF0PMAiPi3m</t>
@@ -307,12 +304,12 @@
     <t>40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
-    <t>24f1GFXCkViGoRpmGqlSSl</t>
-  </si>
-  <si>
     <t>4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
+    <t>1ATL5GLyefJaxhQzSPVrLX</t>
+  </si>
+  <si>
     <t>1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -322,7 +319,7 @@
     <t>59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>1rG5TDs3jYh6OU753I54CI</t>
+    <t>1rknZw4cyL9NInAqSwc8AA</t>
   </si>
   <si>
     <t>0OlIvZ79fagLF0PMAiPi3m</t>
@@ -334,12 +331,12 @@
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2739416ed64daf84936d89e671c'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e029416ed64daf84936d89e671c'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048519416ed64daf84936d89e671c'}]</t>
   </si>
   <si>
-    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273fecaa7826bb0cbe139a8cb83'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02fecaa7826bb0cbe139a8cb83'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851fecaa7826bb0cbe139a8cb83'}]</t>
-  </si>
-  <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2736be9bac15995f089579074de'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e026be9bac15995f089579074de'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048516be9bac15995f089579074de'}]</t>
   </si>
   <si>
+    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273f907de96b9a4fbc04accc0d5'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02f907de96b9a4fbc04accc0d5'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851f907de96b9a4fbc04accc0d5'}]</t>
+  </si>
+  <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273be32d40db35f78b08da18d39'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02be32d40db35f78b08da18d39'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851be32d40db35f78b08da18d39'}]</t>
   </si>
   <si>
@@ -349,7 +346,7 @@
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273aabb223e9fe34e485cc11e02'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02aabb223e9fe34e485cc11e02'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851aabb223e9fe34e485cc11e02'}]</t>
   </si>
   <si>
-    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2737c3bb9f74a98f60bdda6c9a7'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e027c3bb9f74a98f60bdda6c9a7'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048517c3bb9f74a98f60bdda6c9a7'}]</t>
+    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b27358ae8fddecbd2630005409c9'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e0258ae8fddecbd2630005409c9'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d0000485158ae8fddecbd2630005409c9'}]</t>
   </si>
   <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2736e6093d7551f3979d1b2009b'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e026e6093d7551f3979d1b2009b'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048516e6093d7551f3979d1b2009b'}]</t>
@@ -361,37 +358,37 @@
     <t>Views</t>
   </si>
   <si>
-    <t>The Boy Who Played the Harp</t>
-  </si>
-  <si>
     <t>ANTI (Deluxe)</t>
   </si>
   <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
     <t>One Dance (Slowed &amp; Reverb)</t>
   </si>
   <si>
     <t>One Dance (Instrumental)</t>
   </si>
   <si>
-    <t>My World</t>
+    <t>Journals</t>
   </si>
   <si>
     <t>2016-05-06</t>
   </si>
   <si>
-    <t>2025-10-23</t>
-  </si>
-  <si>
     <t>2016-01-28</t>
   </si>
   <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
     <t>2022-01-06</t>
   </si>
   <si>
     <t>2024-04-12</t>
   </si>
   <si>
-    <t>2009-01-01</t>
+    <t>2014-05-13</t>
   </si>
   <si>
     <t>2026-01-23</t>
@@ -406,12 +403,12 @@
     <t>spotify:album:40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
-    <t>spotify:album:24f1GFXCkViGoRpmGqlSSl</t>
-  </si>
-  <si>
     <t>spotify:album:4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
+    <t>spotify:album:1ATL5GLyefJaxhQzSPVrLX</t>
+  </si>
+  <si>
     <t>spotify:album:1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -421,7 +418,7 @@
     <t>spotify:album:59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>spotify:album:1rG5TDs3jYh6OU753I54CI</t>
+    <t>spotify:album:1rknZw4cyL9NInAqSwc8AA</t>
   </si>
   <si>
     <t>spotify:album:0OlIvZ79fagLF0PMAiPi3m</t>
@@ -433,12 +430,12 @@
     <t>USCM51600028</t>
   </si>
   <si>
-    <t>GBUM72506029</t>
-  </si>
-  <si>
     <t>QM5FT1600116</t>
   </si>
   <si>
+    <t>USCM51800004</t>
+  </si>
+  <si>
     <t>USCM51500238</t>
   </si>
   <si>
@@ -448,7 +445,7 @@
     <t>GX8LE2441205</t>
   </si>
   <si>
-    <t>USUM70964274</t>
+    <t>USUM71319306</t>
   </si>
   <si>
     <t>GXD7G2660108</t>
@@ -460,12 +457,12 @@
     <t>https://open.spotify.com/track/1zi7xx7UVEFkmKfv06H8x0</t>
   </si>
   <si>
-    <t>https://open.spotify.com/track/3oTuTpF1F3A7rEC6RKsMRz</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/track/72TFWvU3wUYdUuxejTTIzt</t>
   </si>
   <si>
+    <t>https://open.spotify.com/track/6DCZcSspjsKoFjzjrWoCdn</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/track/0wwPcA6wtMf6HUMpIRdeP7</t>
   </si>
   <si>
@@ -478,7 +475,7 @@
     <t>https://open.spotify.com/track/1OJlaqFVhBObOIY5h9gRGO</t>
   </si>
   <si>
-    <t>https://open.spotify.com/track/6eDApnV9Jdb1nYahOlbbUh</t>
+    <t>https://open.spotify.com/track/3JsydWaf2Ev4ehaLUjj3SY</t>
   </si>
   <si>
     <t>https://open.spotify.com/track/5JytDbvbXv4Ms68VSPgOve</t>
@@ -955,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -967,61 +964,61 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2">
         <v>12</v>
       </c>
       <c r="K2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" t="s">
         <v>63</v>
       </c>
-      <c r="L2" t="s">
-        <v>64</v>
-      </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W2">
         <v>20</v>
       </c>
       <c r="X2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1032,16 +1029,16 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>219743</v>
+        <v>219320</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -1050,61 +1047,61 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -1115,16 +1112,16 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>219320</v>
+        <v>198973</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1133,66 +1130,66 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S4" t="b">
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="X4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1204,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -1216,66 +1213,66 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J5">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W5">
         <v>20</v>
       </c>
       <c r="X5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1287,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1299,61 +1296,61 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="V6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W6">
         <v>1</v>
       </c>
       <c r="X6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1370,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1382,66 +1379,66 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7">
         <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S7" t="b">
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W7">
         <v>20</v>
       </c>
       <c r="X7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1453,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1465,81 +1462,81 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="V8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W8">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>215866</v>
+        <v>248133</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1548,66 +1545,66 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9" t="s">
         <v>62</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>63</v>
-      </c>
       <c r="L9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1619,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1631,66 +1628,66 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
       </c>
       <c r="T10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W10">
         <v>1</v>
       </c>
       <c r="X10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1702,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1714,61 +1711,61 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" t="s">
+        <v>74</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R11" t="s">
+        <v>112</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U11" t="s">
+        <v>126</v>
+      </c>
+      <c r="V11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11" t="s">
         <v>73</v>
       </c>
-      <c r="M11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>104</v>
-      </c>
-      <c r="R11" t="s">
-        <v>113</v>
-      </c>
-      <c r="S11" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U11" t="s">
-        <v>127</v>
-      </c>
-      <c r="V11" t="s">
-        <v>128</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11" t="s">
-        <v>74</v>
-      </c>
       <c r="Y11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Z11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/backend/arq/search_tracks_one_dance.xlsx
+++ b/backend/arq/search_tracks_one_dance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="157">
   <si>
     <t>artists</t>
   </si>
@@ -100,6 +100,9 @@
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/3TVXtAsR1Inumwj472S9r4'}, 'href': 'https://api.spotify.com/v1/artists/3TVXtAsR1Inumwj472S9r4', 'id': '3TVXtAsR1Inumwj472S9r4', 'name': 'Drake', 'type': 'artist', 'uri': 'spotify:artist:3TVXtAsR1Inumwj472S9r4'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/3tVQdUvClmAT7URs9V3rsp'}, 'href': 'https://api.spotify.com/v1/artists/3tVQdUvClmAT7URs9V3rsp', 'id': '3tVQdUvClmAT7URs9V3rsp', 'name': 'Wizkid', 'type': 'artist', 'uri': 'spotify:artist:3tVQdUvClmAT7URs9V3rsp'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/6TK7fjRPdy2GW2pJzNF23L'}, 'href': 'https://api.spotify.com/v1/artists/6TK7fjRPdy2GW2pJzNF23L', 'id': '6TK7fjRPdy2GW2pJzNF23L', 'name': 'Kyla', 'type': 'artist', 'uri': 'spotify:artist:6TK7fjRPdy2GW2pJzNF23L'}]</t>
   </si>
   <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/6Ip8FS7vWT1uKkJSweANQK'}, 'href': 'https://api.spotify.com/v1/artists/6Ip8FS7vWT1uKkJSweANQK', 'id': '6Ip8FS7vWT1uKkJSweANQK', 'name': 'Dave', 'type': 'artist', 'uri': 'spotify:artist:6Ip8FS7vWT1uKkJSweANQK'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/687cZJR45JO7jhk1LHIbgq'}, 'href': 'https://api.spotify.com/v1/artists/687cZJR45JO7jhk1LHIbgq', 'id': '687cZJR45JO7jhk1LHIbgq', 'name': 'Tems', 'type': 'artist', 'uri': 'spotify:artist:687cZJR45JO7jhk1LHIbgq'}]</t>
+  </si>
+  <si>
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/5pKCCKE2ajJHZ9KAiaK11H'}, 'href': 'https://api.spotify.com/v1/artists/5pKCCKE2ajJHZ9KAiaK11H', 'id': '5pKCCKE2ajJHZ9KAiaK11H', 'name': 'Rihanna', 'type': 'artist', 'uri': 'spotify:artist:5pKCCKE2ajJHZ9KAiaK11H'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/3TVXtAsR1Inumwj472S9r4'}, 'href': 'https://api.spotify.com/v1/artists/3TVXtAsR1Inumwj472S9r4', 'id': '3TVXtAsR1Inumwj472S9r4', 'name': 'Drake', 'type': 'artist', 'uri': 'spotify:artist:3TVXtAsR1Inumwj472S9r4'}]</t>
   </si>
   <si>
@@ -112,7 +115,7 @@
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/16R2MLhKVi8GXUYSW8WoXD'}, 'href': 'https://api.spotify.com/v1/artists/16R2MLhKVi8GXUYSW8WoXD', 'id': '16R2MLhKVi8GXUYSW8WoXD', 'name': 'Fironn', 'type': 'artist', 'uri': 'spotify:artist:16R2MLhKVi8GXUYSW8WoXD'}]</t>
   </si>
   <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1uNFoZAHBGtllmzznpCI3s'}, 'href': 'https://api.spotify.com/v1/artists/1uNFoZAHBGtllmzznpCI3s', 'id': '1uNFoZAHBGtllmzznpCI3s', 'name': 'Justin Bieber', 'type': 'artist', 'uri': 'spotify:artist:1uNFoZAHBGtllmzznpCI3s'}, {'external_urls': {'spotify': 'https://open.spotify.com/artist/1anyVhU62p31KFi8MEzkbf'}, 'href': 'https://api.spotify.com/v1/artists/1anyVhU62p31KFi8MEzkbf', 'id': '1anyVhU62p31KFi8MEzkbf', 'name': 'Chance the Rapper', 'type': 'artist', 'uri': 'spotify:artist:1anyVhU62p31KFi8MEzkbf'}]</t>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1uNFoZAHBGtllmzznpCI3s'}, 'href': 'https://api.spotify.com/v1/artists/1uNFoZAHBGtllmzznpCI3s', 'id': '1uNFoZAHBGtllmzznpCI3s', 'name': 'Justin Bieber', 'type': 'artist', 'uri': 'spotify:artist:1uNFoZAHBGtllmzznpCI3s'}]</t>
   </si>
   <si>
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1sPYSDiyubB8fkWvh3iFdr'}, 'href': 'https://api.spotify.com/v1/artists/1sPYSDiyubB8fkWvh3iFdr', 'id': '1sPYSDiyubB8fkWvh3iFdr', 'name': 'Leo Walt', 'type': 'artist', 'uri': 'spotify:artist:1sPYSDiyubB8fkWvh3iFdr'}]</t>
@@ -124,12 +127,12 @@
     <t>https://api.spotify.com/v1/tracks/1zi7xx7UVEFkmKfv06H8x0</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/tracks/3oTuTpF1F3A7rEC6RKsMRz</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/tracks/72TFWvU3wUYdUuxejTTIzt</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/tracks/6DCZcSspjsKoFjzjrWoCdn</t>
-  </si>
-  <si>
     <t>https://api.spotify.com/v1/tracks/0wwPcA6wtMf6HUMpIRdeP7</t>
   </si>
   <si>
@@ -142,7 +145,7 @@
     <t>https://api.spotify.com/v1/tracks/1OJlaqFVhBObOIY5h9gRGO</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/tracks/3JsydWaf2Ev4ehaLUjj3SY</t>
+    <t>https://api.spotify.com/v1/tracks/6eDApnV9Jdb1nYahOlbbUh</t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/tracks/5JytDbvbXv4Ms68VSPgOve</t>
@@ -154,12 +157,12 @@
     <t>1zi7xx7UVEFkmKfv06H8x0</t>
   </si>
   <si>
+    <t>3oTuTpF1F3A7rEC6RKsMRz</t>
+  </si>
+  <si>
     <t>72TFWvU3wUYdUuxejTTIzt</t>
   </si>
   <si>
-    <t>6DCZcSspjsKoFjzjrWoCdn</t>
-  </si>
-  <si>
     <t>0wwPcA6wtMf6HUMpIRdeP7</t>
   </si>
   <si>
@@ -172,7 +175,7 @@
     <t>1OJlaqFVhBObOIY5h9gRGO</t>
   </si>
   <si>
-    <t>3JsydWaf2Ev4ehaLUjj3SY</t>
+    <t>6eDApnV9Jdb1nYahOlbbUh</t>
   </si>
   <si>
     <t>5JytDbvbXv4Ms68VSPgOve</t>
@@ -184,12 +187,12 @@
     <t>One Dance</t>
   </si>
   <si>
+    <t>Raindance (feat. Tems)</t>
+  </si>
+  <si>
     <t>Work</t>
   </si>
   <si>
-    <t>God's Plan</t>
-  </si>
-  <si>
     <t>Hotline Bling</t>
   </si>
   <si>
@@ -199,7 +202,7 @@
     <t>One Dance - Instrumental Best Part Slowed</t>
   </si>
   <si>
-    <t>Confident</t>
+    <t>One Time</t>
   </si>
   <si>
     <t>track</t>
@@ -208,12 +211,12 @@
     <t>spotify:track:1zi7xx7UVEFkmKfv06H8x0</t>
   </si>
   <si>
+    <t>spotify:track:3oTuTpF1F3A7rEC6RKsMRz</t>
+  </si>
+  <si>
     <t>spotify:track:72TFWvU3wUYdUuxejTTIzt</t>
   </si>
   <si>
-    <t>spotify:track:6DCZcSspjsKoFjzjrWoCdn</t>
-  </si>
-  <si>
     <t>spotify:track:0wwPcA6wtMf6HUMpIRdeP7</t>
   </si>
   <si>
@@ -226,7 +229,7 @@
     <t>spotify:track:1OJlaqFVhBObOIY5h9gRGO</t>
   </si>
   <si>
-    <t>spotify:track:3JsydWaf2Ev4ehaLUjj3SY</t>
+    <t>spotify:track:6eDApnV9Jdb1nYahOlbbUh</t>
   </si>
   <si>
     <t>spotify:track:5JytDbvbXv4Ms68VSPgOve</t>
@@ -241,21 +244,21 @@
     <t>single</t>
   </si>
   <si>
+    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/6Ip8FS7vWT1uKkJSweANQK'}, 'href': 'https://api.spotify.com/v1/artists/6Ip8FS7vWT1uKkJSweANQK', 'id': '6Ip8FS7vWT1uKkJSweANQK', 'name': 'Dave', 'type': 'artist', 'uri': 'spotify:artist:6Ip8FS7vWT1uKkJSweANQK'}]</t>
+  </si>
+  <si>
     <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/5pKCCKE2ajJHZ9KAiaK11H'}, 'href': 'https://api.spotify.com/v1/artists/5pKCCKE2ajJHZ9KAiaK11H', 'id': '5pKCCKE2ajJHZ9KAiaK11H', 'name': 'Rihanna', 'type': 'artist', 'uri': 'spotify:artist:5pKCCKE2ajJHZ9KAiaK11H'}]</t>
   </si>
   <si>
-    <t>[{'external_urls': {'spotify': 'https://open.spotify.com/artist/1uNFoZAHBGtllmzznpCI3s'}, 'href': 'https://api.spotify.com/v1/artists/1uNFoZAHBGtllmzznpCI3s', 'id': '1uNFoZAHBGtllmzznpCI3s', 'name': 'Justin Bieber', 'type': 'artist', 'uri': 'spotify:artist:1uNFoZAHBGtllmzznpCI3s'}]</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/album/40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
+    <t>https://open.spotify.com/album/24f1GFXCkViGoRpmGqlSSl</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/album/4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
-    <t>https://open.spotify.com/album/1ATL5GLyefJaxhQzSPVrLX</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/album/1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -265,7 +268,7 @@
     <t>https://open.spotify.com/album/59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>https://open.spotify.com/album/1rknZw4cyL9NInAqSwc8AA</t>
+    <t>https://open.spotify.com/album/1rG5TDs3jYh6OU753I54CI</t>
   </si>
   <si>
     <t>https://open.spotify.com/album/0OlIvZ79fagLF0PMAiPi3m</t>
@@ -277,12 +280,12 @@
     <t>https://api.spotify.com/v1/albums/40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/albums/24f1GFXCkViGoRpmGqlSSl</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/albums/4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/albums/1ATL5GLyefJaxhQzSPVrLX</t>
-  </si>
-  <si>
     <t>https://api.spotify.com/v1/albums/1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -292,7 +295,7 @@
     <t>https://api.spotify.com/v1/albums/59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/albums/1rknZw4cyL9NInAqSwc8AA</t>
+    <t>https://api.spotify.com/v1/albums/1rG5TDs3jYh6OU753I54CI</t>
   </si>
   <si>
     <t>https://api.spotify.com/v1/albums/0OlIvZ79fagLF0PMAiPi3m</t>
@@ -304,12 +307,12 @@
     <t>40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
+    <t>24f1GFXCkViGoRpmGqlSSl</t>
+  </si>
+  <si>
     <t>4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
-    <t>1ATL5GLyefJaxhQzSPVrLX</t>
-  </si>
-  <si>
     <t>1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -319,7 +322,7 @@
     <t>59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>1rknZw4cyL9NInAqSwc8AA</t>
+    <t>1rG5TDs3jYh6OU753I54CI</t>
   </si>
   <si>
     <t>0OlIvZ79fagLF0PMAiPi3m</t>
@@ -331,12 +334,12 @@
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2739416ed64daf84936d89e671c'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e029416ed64daf84936d89e671c'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048519416ed64daf84936d89e671c'}]</t>
   </si>
   <si>
+    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273fecaa7826bb0cbe139a8cb83'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02fecaa7826bb0cbe139a8cb83'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851fecaa7826bb0cbe139a8cb83'}]</t>
+  </si>
+  <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2736be9bac15995f089579074de'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e026be9bac15995f089579074de'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048516be9bac15995f089579074de'}]</t>
   </si>
   <si>
-    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273f907de96b9a4fbc04accc0d5'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02f907de96b9a4fbc04accc0d5'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851f907de96b9a4fbc04accc0d5'}]</t>
-  </si>
-  <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273be32d40db35f78b08da18d39'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02be32d40db35f78b08da18d39'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851be32d40db35f78b08da18d39'}]</t>
   </si>
   <si>
@@ -346,7 +349,7 @@
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b273aabb223e9fe34e485cc11e02'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e02aabb223e9fe34e485cc11e02'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d00004851aabb223e9fe34e485cc11e02'}]</t>
   </si>
   <si>
-    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b27358ae8fddecbd2630005409c9'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e0258ae8fddecbd2630005409c9'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d0000485158ae8fddecbd2630005409c9'}]</t>
+    <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2737c3bb9f74a98f60bdda6c9a7'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e027c3bb9f74a98f60bdda6c9a7'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048517c3bb9f74a98f60bdda6c9a7'}]</t>
   </si>
   <si>
     <t>[{'height': 640, 'width': 640, 'url': 'https://i.scdn.co/image/ab67616d0000b2736e6093d7551f3979d1b2009b'}, {'height': 300, 'width': 300, 'url': 'https://i.scdn.co/image/ab67616d00001e026e6093d7551f3979d1b2009b'}, {'height': 64, 'width': 64, 'url': 'https://i.scdn.co/image/ab67616d000048516e6093d7551f3979d1b2009b'}]</t>
@@ -358,37 +361,37 @@
     <t>Views</t>
   </si>
   <si>
+    <t>The Boy Who Played the Harp</t>
+  </si>
+  <si>
     <t>ANTI (Deluxe)</t>
   </si>
   <si>
-    <t>Scorpion</t>
-  </si>
-  <si>
     <t>One Dance (Slowed &amp; Reverb)</t>
   </si>
   <si>
     <t>One Dance (Instrumental)</t>
   </si>
   <si>
-    <t>Journals</t>
+    <t>My World</t>
   </si>
   <si>
     <t>2016-05-06</t>
   </si>
   <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
     <t>2016-01-28</t>
   </si>
   <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
     <t>2022-01-06</t>
   </si>
   <si>
     <t>2024-04-12</t>
   </si>
   <si>
-    <t>2014-05-13</t>
+    <t>2009-01-01</t>
   </si>
   <si>
     <t>2026-01-23</t>
@@ -403,12 +406,12 @@
     <t>spotify:album:40GMAhriYJRO1rsY4YdrZb</t>
   </si>
   <si>
+    <t>spotify:album:24f1GFXCkViGoRpmGqlSSl</t>
+  </si>
+  <si>
     <t>spotify:album:4UlGauD7ROb3YbVOFMgW5u</t>
   </si>
   <si>
-    <t>spotify:album:1ATL5GLyefJaxhQzSPVrLX</t>
-  </si>
-  <si>
     <t>spotify:album:1JqWkYsWASxnZb1owdexHp</t>
   </si>
   <si>
@@ -418,7 +421,7 @@
     <t>spotify:album:59RTmHc6JY3XPuuMfkfrlD</t>
   </si>
   <si>
-    <t>spotify:album:1rknZw4cyL9NInAqSwc8AA</t>
+    <t>spotify:album:1rG5TDs3jYh6OU753I54CI</t>
   </si>
   <si>
     <t>spotify:album:0OlIvZ79fagLF0PMAiPi3m</t>
@@ -430,12 +433,12 @@
     <t>USCM51600028</t>
   </si>
   <si>
+    <t>GBUM72506029</t>
+  </si>
+  <si>
     <t>QM5FT1600116</t>
   </si>
   <si>
-    <t>USCM51800004</t>
-  </si>
-  <si>
     <t>USCM51500238</t>
   </si>
   <si>
@@ -445,7 +448,7 @@
     <t>GX8LE2441205</t>
   </si>
   <si>
-    <t>USUM71319306</t>
+    <t>USUM70964274</t>
   </si>
   <si>
     <t>GXD7G2660108</t>
@@ -457,12 +460,12 @@
     <t>https://open.spotify.com/track/1zi7xx7UVEFkmKfv06H8x0</t>
   </si>
   <si>
+    <t>https://open.spotify.com/track/3oTuTpF1F3A7rEC6RKsMRz</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/track/72TFWvU3wUYdUuxejTTIzt</t>
   </si>
   <si>
-    <t>https://open.spotify.com/track/6DCZcSspjsKoFjzjrWoCdn</t>
-  </si>
-  <si>
     <t>https://open.spotify.com/track/0wwPcA6wtMf6HUMpIRdeP7</t>
   </si>
   <si>
@@ -475,7 +478,7 @@
     <t>https://open.spotify.com/track/1OJlaqFVhBObOIY5h9gRGO</t>
   </si>
   <si>
-    <t>https://open.spotify.com/track/3JsydWaf2Ev4ehaLUjj3SY</t>
+    <t>https://open.spotify.com/track/6eDApnV9Jdb1nYahOlbbUh</t>
   </si>
   <si>
     <t>https://open.spotify.com/track/5JytDbvbXv4Ms68VSPgOve</t>
@@ -952,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -964,61 +967,61 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J2">
         <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W2">
         <v>20</v>
       </c>
       <c r="X2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1029,16 +1032,16 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>219320</v>
+        <v>219743</v>
       </c>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -1047,61 +1050,61 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="V3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -1112,16 +1115,16 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>198973</v>
+        <v>219320</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1130,66 +1133,66 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S4" t="b">
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="X4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1201,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -1213,66 +1216,66 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W5">
         <v>20</v>
       </c>
       <c r="X5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1284,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1296,61 +1299,61 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>99</v>
+      </c>
+      <c r="R6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>117</v>
+      </c>
+      <c r="U6" t="s">
+        <v>123</v>
+      </c>
+      <c r="V6" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6" t="s">
         <v>74</v>
       </c>
-      <c r="N6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>98</v>
-      </c>
-      <c r="R6" t="s">
-        <v>107</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
-        <v>116</v>
-      </c>
-      <c r="U6" t="s">
-        <v>122</v>
-      </c>
-      <c r="V6" t="s">
-        <v>127</v>
-      </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6" t="s">
-        <v>73</v>
-      </c>
       <c r="Y6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1367,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1379,66 +1382,66 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J7">
         <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S7" t="b">
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W7">
         <v>20</v>
       </c>
       <c r="X7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1450,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1462,81 +1465,81 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="V8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W8">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>248133</v>
+        <v>215866</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1545,66 +1548,66 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="V9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1616,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1628,66 +1631,66 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>103</v>
+      </c>
+      <c r="R10" t="s">
+        <v>112</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="s">
+        <v>56</v>
+      </c>
+      <c r="U10" t="s">
+        <v>126</v>
+      </c>
+      <c r="V10" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10" t="s">
         <v>74</v>
       </c>
-      <c r="N10" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" t="s">
-        <v>111</v>
-      </c>
-      <c r="S10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" t="s">
-        <v>55</v>
-      </c>
-      <c r="U10" t="s">
-        <v>125</v>
-      </c>
-      <c r="V10" t="s">
-        <v>127</v>
-      </c>
-      <c r="W10">
-        <v>1</v>
-      </c>
-      <c r="X10" t="s">
-        <v>73</v>
-      </c>
       <c r="Y10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1699,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1711,61 +1714,61 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="s">
+        <v>56</v>
+      </c>
+      <c r="U11" t="s">
+        <v>127</v>
+      </c>
+      <c r="V11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11" t="s">
         <v>74</v>
       </c>
-      <c r="N11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" t="s">
-        <v>112</v>
-      </c>
-      <c r="S11" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" t="s">
-        <v>55</v>
-      </c>
-      <c r="U11" t="s">
-        <v>126</v>
-      </c>
-      <c r="V11" t="s">
-        <v>127</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11" t="s">
-        <v>73</v>
-      </c>
       <c r="Y11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Z11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
